--- a/data/LME_061/LME_061.xlsx
+++ b/data/LME_061/LME_061.xlsx
@@ -10,8 +10,12 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="PPR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NPP" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +40,22 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +81,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -434,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,108 +532,104 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>catch years</t>
+          <t>model workbooks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1981-2019</t>
+          <t>none yet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>taxa in catch</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>14</v>
+          <t>catch years</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1981-2019</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>taxa in catch</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>taxa with a trophic level</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model source context</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No pilot model selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>catch_tonnes</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>ppr_tonnes</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>ppr_over_npp_percent</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B13" t="n">
-        <v>48.876</v>
-      </c>
-      <c r="C13" t="n">
-        <v>8300.387000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0173</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C14" t="n">
-        <v>492.442</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1997</v>
+        <v>1981</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002</v>
+        <v>48.876</v>
       </c>
       <c r="C15" t="n">
-        <v>0.376</v>
+        <v>8300.387000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1998</v>
+        <v>1982</v>
       </c>
       <c r="B16" t="n">
-        <v>0.112</v>
+        <v>2.9</v>
       </c>
       <c r="C16" t="n">
-        <v>43.398</v>
+        <v>492.442</v>
       </c>
       <c r="D16" t="n">
         <v>0.0001</v>
@@ -621,279 +637,279 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B17" t="n">
-        <v>1.354</v>
+        <v>0.002</v>
       </c>
       <c r="C17" t="n">
-        <v>334.065</v>
+        <v>0.376</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B18" t="n">
-        <v>4.235</v>
+        <v>0.112</v>
       </c>
       <c r="C18" t="n">
-        <v>1066.502</v>
+        <v>43.398</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="B19" t="n">
-        <v>26.636</v>
+        <v>1.354</v>
       </c>
       <c r="C19" t="n">
-        <v>7778.429</v>
+        <v>334.065</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0162</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="B20" t="n">
-        <v>84.185</v>
+        <v>4.235</v>
       </c>
       <c r="C20" t="n">
-        <v>24772.295</v>
+        <v>1066.502</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0517</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="B21" t="n">
-        <v>31.189</v>
+        <v>26.636</v>
       </c>
       <c r="C21" t="n">
-        <v>9116.116</v>
+        <v>7778.429</v>
       </c>
       <c r="D21" t="n">
-        <v>0.019</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="B22" t="n">
-        <v>89.81699999999999</v>
+        <v>84.185</v>
       </c>
       <c r="C22" t="n">
-        <v>26450.41</v>
+        <v>24772.295</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0553</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B23" t="n">
-        <v>86.32899999999999</v>
+        <v>31.189</v>
       </c>
       <c r="C23" t="n">
-        <v>25438.287</v>
+        <v>9116.116</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0531</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B24" t="n">
-        <v>33.885</v>
+        <v>89.81699999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>9977.075999999999</v>
+        <v>26450.41</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0208</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B25" t="n">
-        <v>33.623</v>
+        <v>86.32899999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>9835.6</v>
+        <v>25438.287</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0205</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B26" t="n">
-        <v>32.515</v>
+        <v>33.885</v>
       </c>
       <c r="C26" t="n">
-        <v>9542.541999999999</v>
+        <v>9977.075999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0199</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B27" t="n">
-        <v>43.296</v>
+        <v>33.623</v>
       </c>
       <c r="C27" t="n">
-        <v>12756.106</v>
+        <v>9835.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0266</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B28" t="n">
-        <v>41.405</v>
+        <v>32.515</v>
       </c>
       <c r="C28" t="n">
-        <v>12202.314</v>
+        <v>9542.541999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0255</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B29" t="n">
-        <v>5.806</v>
+        <v>43.296</v>
       </c>
       <c r="C29" t="n">
-        <v>1699.122</v>
+        <v>12756.106</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0035</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B30" t="n">
-        <v>8.305999999999999</v>
+        <v>41.405</v>
       </c>
       <c r="C30" t="n">
-        <v>2453.623</v>
+        <v>12202.314</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0051</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B31" t="n">
-        <v>9.73</v>
+        <v>5.806</v>
       </c>
       <c r="C31" t="n">
-        <v>2864.426</v>
+        <v>1699.122</v>
       </c>
       <c r="D31" t="n">
-        <v>0.006</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B32" t="n">
-        <v>0.174</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>45.691</v>
+        <v>2453.623</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B33" t="n">
-        <v>2.679</v>
+        <v>9.73</v>
       </c>
       <c r="C33" t="n">
-        <v>790.777</v>
+        <v>2864.426</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0017</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B34" t="n">
-        <v>5.972</v>
+        <v>0.174</v>
       </c>
       <c r="C34" t="n">
-        <v>1749.998</v>
+        <v>45.691</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B35" t="n">
-        <v>0.004</v>
+        <v>2.679</v>
       </c>
       <c r="C35" t="n">
-        <v>0.67</v>
+        <v>790.777</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B36" t="n">
-        <v>0.714</v>
+        <v>5.972</v>
       </c>
       <c r="C36" t="n">
-        <v>201.538</v>
+        <v>1749.998</v>
       </c>
       <c r="D36" t="n">
         <v>0.0004</v>
@@ -901,16 +917,51 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B37" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="C38" t="n">
+        <v>201.538</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>2019</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B39" t="n">
         <v>0.25</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C39" t="n">
         <v>57.733</v>
       </c>
-      <c r="D37" t="n">
-        <v>0.0001</v>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -979,130 +1030,80 @@
           <t>commercial_group</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="T1" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="U1" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="V1" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="Y1" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="Z1" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="AA1" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="AB1" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AC1" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="E1" s="2" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1997</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="L1" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="Q1" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="R1" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="S1" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="T1" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="U1" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="V1" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="W1" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="X1" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="Y1" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="Z1" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA1" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AB1" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AC1" s="2" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="2">
@@ -2665,6 +2666,245 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: all</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: inner</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Recycling diagnostics from diagnose_sppr()</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>b: detrital recycling; rho living: living food-web cycles. Each must be below 1 for convergence; these are necessary, not sufficient checks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>TE_option</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>rho living</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>diagnostic status</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>b converges</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>living converges</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>input balanced</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2753,130 +2993,80 @@
           <t>trophic_level</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1997</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1982</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1997</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1998</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="5">
@@ -3734,7 +3924,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/LME_061/LME_061.xlsx
+++ b/data/LME_061/LME_061.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Catch" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SPPR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="sppr_all" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="sppr_inner" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sppr_PP" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Recycling" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="PPR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="NPP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Final mappings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SPPR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="sppr_all" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="sppr_inner" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="sppr_PP" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Recycling" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PPR" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="NPP" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'NPP'!$A$3:$O$28</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,13 +457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -617,9 +620,6 @@
       <c r="C15" t="n">
         <v>8300.387000000001</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.0019</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -631,9 +631,6 @@
       <c r="C16" t="n">
         <v>492.442</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.0001</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -645,9 +642,6 @@
       <c r="C17" t="n">
         <v>0.376</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -674,7 +668,7 @@
         <v>334.065</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -688,7 +682,7 @@
         <v>1066.502</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +696,7 @@
         <v>7778.429</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0018</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="22">
@@ -716,7 +710,7 @@
         <v>24772.295</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0057</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="23">
@@ -730,7 +724,7 @@
         <v>9116.116</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0021</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="24">
@@ -744,7 +738,7 @@
         <v>26450.41</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0061</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="25">
@@ -758,7 +752,7 @@
         <v>25438.287</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0059</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="26">
@@ -772,7 +766,7 @@
         <v>9977.075999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0023</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="27">
@@ -786,7 +780,7 @@
         <v>9835.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0023</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="28">
@@ -800,7 +794,7 @@
         <v>9542.541999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0022</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="29">
@@ -814,7 +808,7 @@
         <v>12756.106</v>
       </c>
       <c r="D29" t="n">
-        <v>0.003</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="30">
@@ -828,7 +822,7 @@
         <v>12202.314</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0028</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="31">
@@ -842,7 +836,7 @@
         <v>1699.122</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="32">
@@ -856,7 +850,7 @@
         <v>2453.623</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="33">
@@ -870,7 +864,7 @@
         <v>2864.426</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="34">
@@ -898,7 +892,7 @@
         <v>790.777</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="36">
@@ -912,7 +906,7 @@
         <v>1749.998</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="37">
@@ -960,11 +954,1330 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PPR/NPP converts wet-weight PP to carbon at 9:1; NPP is the fixed 2019 ensemble median.</t>
+          <t>PPR/NPP converts wet-weight PP to carbon at 9:1 and uses the matching year's NPP ensemble median.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PPR/NPP is blank for years without NPP; see NPP for availability and provenance.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="75" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Annual net primary production, tonnes carbon per year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PPR/NPP uses the ensemble median for the matching catch year. Blank values are unavailable; no year is substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>npp_antoinemorel_tC_yr</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>npp_vgpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>npp_eppley_tC_yr</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cbpm_tC_yr</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>npp_cafe_tC_yr</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>ens_median_tC_yr</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>ens_min_tC_yr</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>ens_max_tC_yr</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>n_models</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>available_models</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>ensemble_basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1981</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1997</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unsupported</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>reference source has no complete twelve-month year</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>141884062.2813387</v>
+      </c>
+      <c r="G7" t="n">
+        <v>141884062.2813387</v>
+      </c>
+      <c r="H7" t="n">
+        <v>141884062.2813387</v>
+      </c>
+      <c r="I7" t="n">
+        <v>141884062.2813387</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1998/65dfd93f461846d2/provenance.json</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B8" t="n">
+        <v>148449202.4111406</v>
+      </c>
+      <c r="G8" t="n">
+        <v>148449202.4111406</v>
+      </c>
+      <c r="H8" t="n">
+        <v>148449202.4111406</v>
+      </c>
+      <c r="I8" t="n">
+        <v>148449202.4111406</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/1999/4b1cb2d6cba203fb/provenance.json</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B9" t="n">
+        <v>172056884.8675973</v>
+      </c>
+      <c r="G9" t="n">
+        <v>172056884.8675973</v>
+      </c>
+      <c r="H9" t="n">
+        <v>172056884.8675973</v>
+      </c>
+      <c r="I9" t="n">
+        <v>172056884.8675973</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2000/4bea86f4cd09bd55/provenance.json</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B10" t="n">
+        <v>131680194.3975324</v>
+      </c>
+      <c r="G10" t="n">
+        <v>131680194.3975324</v>
+      </c>
+      <c r="H10" t="n">
+        <v>131680194.3975324</v>
+      </c>
+      <c r="I10" t="n">
+        <v>131680194.3975324</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2001/0ec8617947fb90b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B11" t="n">
+        <v>127249885.8869314</v>
+      </c>
+      <c r="G11" t="n">
+        <v>127249885.8869314</v>
+      </c>
+      <c r="H11" t="n">
+        <v>127249885.8869314</v>
+      </c>
+      <c r="I11" t="n">
+        <v>127249885.8869314</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vgpm: unsupported_year; eppley: unsupported_year; cbpm: unsupported_year; cafe: unsupported_year</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2002/3789d747c9365882/provenance.json</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>antoinemorel</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106557948.0944044</v>
+      </c>
+      <c r="C12" t="n">
+        <v>79384309.46569002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>84277000.3221619</v>
+      </c>
+      <c r="E12" t="n">
+        <v>115501252.0733541</v>
+      </c>
+      <c r="F12" t="n">
+        <v>148428937.2270784</v>
+      </c>
+      <c r="G12" t="n">
+        <v>106557948.0944044</v>
+      </c>
+      <c r="H12" t="n">
+        <v>79384309.46569002</v>
+      </c>
+      <c r="I12" t="n">
+        <v>148428937.2270784</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2003/c3a820791e3378ef/provenance.json</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107546979.8200809</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86607481.55659851</v>
+      </c>
+      <c r="D13" t="n">
+        <v>95735678.92682473</v>
+      </c>
+      <c r="E13" t="n">
+        <v>112874671.1298498</v>
+      </c>
+      <c r="F13" t="n">
+        <v>144004980.417264</v>
+      </c>
+      <c r="G13" t="n">
+        <v>107546979.8200809</v>
+      </c>
+      <c r="H13" t="n">
+        <v>86607481.55659851</v>
+      </c>
+      <c r="I13" t="n">
+        <v>144004980.417264</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2004/f4cd3b4c7fc3dd8b/provenance.json</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99549696.9787605</v>
+      </c>
+      <c r="C14" t="n">
+        <v>76049779.91199407</v>
+      </c>
+      <c r="D14" t="n">
+        <v>82786977.19707571</v>
+      </c>
+      <c r="E14" t="n">
+        <v>99102264.47358903</v>
+      </c>
+      <c r="F14" t="n">
+        <v>129358400.732069</v>
+      </c>
+      <c r="G14" t="n">
+        <v>99102264.47358903</v>
+      </c>
+      <c r="H14" t="n">
+        <v>76049779.91199407</v>
+      </c>
+      <c r="I14" t="n">
+        <v>129358400.732069</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2005/4bdcca026379c2bd/provenance.json</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104885062.6007321</v>
+      </c>
+      <c r="C15" t="n">
+        <v>85621851.6261138</v>
+      </c>
+      <c r="D15" t="n">
+        <v>91495219.0320881</v>
+      </c>
+      <c r="E15" t="n">
+        <v>107624470.7298333</v>
+      </c>
+      <c r="F15" t="n">
+        <v>130074212.1175894</v>
+      </c>
+      <c r="G15" t="n">
+        <v>104885062.6007321</v>
+      </c>
+      <c r="H15" t="n">
+        <v>85621851.6261138</v>
+      </c>
+      <c r="I15" t="n">
+        <v>130074212.1175894</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2006/3ea13e28f3d7c994/provenance.json</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97905492.15267308</v>
+      </c>
+      <c r="C16" t="n">
+        <v>73710120.74192545</v>
+      </c>
+      <c r="D16" t="n">
+        <v>81469851.14907902</v>
+      </c>
+      <c r="E16" t="n">
+        <v>88795577.5191813</v>
+      </c>
+      <c r="F16" t="n">
+        <v>121773962.4446425</v>
+      </c>
+      <c r="G16" t="n">
+        <v>88795577.5191813</v>
+      </c>
+      <c r="H16" t="n">
+        <v>73710120.74192545</v>
+      </c>
+      <c r="I16" t="n">
+        <v>121773962.4446425</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2007/af2057f32254ca19/provenance.json</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90841062.45028712</v>
+      </c>
+      <c r="C17" t="n">
+        <v>71150341.45470637</v>
+      </c>
+      <c r="D17" t="n">
+        <v>78628877.92452721</v>
+      </c>
+      <c r="E17" t="n">
+        <v>90750393.8456464</v>
+      </c>
+      <c r="F17" t="n">
+        <v>126299597.5793026</v>
+      </c>
+      <c r="G17" t="n">
+        <v>90750393.8456464</v>
+      </c>
+      <c r="H17" t="n">
+        <v>71150341.45470637</v>
+      </c>
+      <c r="I17" t="n">
+        <v>126299597.5793026</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2008/51e4a448b1f4148f/provenance.json</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98512791.47745189</v>
+      </c>
+      <c r="C18" t="n">
+        <v>83695891.55941193</v>
+      </c>
+      <c r="D18" t="n">
+        <v>91498388.87064937</v>
+      </c>
+      <c r="E18" t="n">
+        <v>94931953.02102947</v>
+      </c>
+      <c r="F18" t="n">
+        <v>134260618.2373303</v>
+      </c>
+      <c r="G18" t="n">
+        <v>94931953.02102947</v>
+      </c>
+      <c r="H18" t="n">
+        <v>83695891.55941193</v>
+      </c>
+      <c r="I18" t="n">
+        <v>134260618.2373303</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2009/d16425bc4ac9cb7d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>5</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B19" t="n">
+        <v>108870584.9965542</v>
+      </c>
+      <c r="C19" t="n">
+        <v>94055989.4887848</v>
+      </c>
+      <c r="D19" t="n">
+        <v>103056194.7312692</v>
+      </c>
+      <c r="E19" t="n">
+        <v>90317553.84382756</v>
+      </c>
+      <c r="F19" t="n">
+        <v>135416007.7386802</v>
+      </c>
+      <c r="G19" t="n">
+        <v>103056194.7312692</v>
+      </c>
+      <c r="H19" t="n">
+        <v>90317553.84382756</v>
+      </c>
+      <c r="I19" t="n">
+        <v>135416007.7386802</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2010/5d2cc2c9685a81c9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105032497.7595431</v>
+      </c>
+      <c r="C20" t="n">
+        <v>85490316.78774421</v>
+      </c>
+      <c r="D20" t="n">
+        <v>92589992.39660808</v>
+      </c>
+      <c r="E20" t="n">
+        <v>96077853.69335242</v>
+      </c>
+      <c r="F20" t="n">
+        <v>139071043.7269942</v>
+      </c>
+      <c r="G20" t="n">
+        <v>96077853.69335242</v>
+      </c>
+      <c r="H20" t="n">
+        <v>85490316.78774421</v>
+      </c>
+      <c r="I20" t="n">
+        <v>139071043.7269942</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2011/a6c24b780ceeb354/provenance.json</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95844328.79087457</v>
+      </c>
+      <c r="C21" t="n">
+        <v>84022479.78745846</v>
+      </c>
+      <c r="D21" t="n">
+        <v>92433256.14366572</v>
+      </c>
+      <c r="E21" t="n">
+        <v>86148682.39610271</v>
+      </c>
+      <c r="F21" t="n">
+        <v>140309767.3878974</v>
+      </c>
+      <c r="G21" t="n">
+        <v>92433256.14366572</v>
+      </c>
+      <c r="H21" t="n">
+        <v>84022479.78745846</v>
+      </c>
+      <c r="I21" t="n">
+        <v>140309767.3878974</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2012/2fd3c52e363d2259/provenance.json</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>5</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91480771.47288294</v>
+      </c>
+      <c r="C22" t="n">
+        <v>85120675.22186717</v>
+      </c>
+      <c r="D22" t="n">
+        <v>91237022.58732818</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90365221.64020632</v>
+      </c>
+      <c r="F22" t="n">
+        <v>131877299.5358466</v>
+      </c>
+      <c r="G22" t="n">
+        <v>91237022.58732818</v>
+      </c>
+      <c r="H22" t="n">
+        <v>85120675.22186717</v>
+      </c>
+      <c r="I22" t="n">
+        <v>131877299.5358466</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2013/821becabd572bab5/provenance.json</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97435692.58467382</v>
+      </c>
+      <c r="C23" t="n">
+        <v>83217439.56422487</v>
+      </c>
+      <c r="D23" t="n">
+        <v>91264583.61078274</v>
+      </c>
+      <c r="E23" t="n">
+        <v>94723724.06767926</v>
+      </c>
+      <c r="F23" t="n">
+        <v>140333784.4817224</v>
+      </c>
+      <c r="G23" t="n">
+        <v>94723724.06767926</v>
+      </c>
+      <c r="H23" t="n">
+        <v>83217439.56422487</v>
+      </c>
+      <c r="I23" t="n">
+        <v>140333784.4817224</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2014/c9d1725dde41256d/provenance.json</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B24" t="n">
+        <v>108031644.1390299</v>
+      </c>
+      <c r="C24" t="n">
+        <v>89777170.44551624</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100652869.5693805</v>
+      </c>
+      <c r="E24" t="n">
+        <v>73330407.91029309</v>
+      </c>
+      <c r="F24" t="n">
+        <v>139349766.203254</v>
+      </c>
+      <c r="G24" t="n">
+        <v>100652869.5693805</v>
+      </c>
+      <c r="H24" t="n">
+        <v>73330407.91029309</v>
+      </c>
+      <c r="I24" t="n">
+        <v>139349766.203254</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2015/9d39afaaa8b014f8/provenance.json</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B25" t="n">
+        <v>115416286.9082317</v>
+      </c>
+      <c r="C25" t="n">
+        <v>93048889.17241141</v>
+      </c>
+      <c r="D25" t="n">
+        <v>105358593.1685093</v>
+      </c>
+      <c r="E25" t="n">
+        <v>69708622.38031742</v>
+      </c>
+      <c r="F25" t="n">
+        <v>149221871.6577978</v>
+      </c>
+      <c r="G25" t="n">
+        <v>105358593.1685093</v>
+      </c>
+      <c r="H25" t="n">
+        <v>69708622.38031742</v>
+      </c>
+      <c r="I25" t="n">
+        <v>149221871.6577978</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2016/cfbe2d742214e408/provenance.json</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101952799.098096</v>
+      </c>
+      <c r="C26" t="n">
+        <v>92990384.1718502</v>
+      </c>
+      <c r="D26" t="n">
+        <v>99359777.75507279</v>
+      </c>
+      <c r="E26" t="n">
+        <v>73521643.66348314</v>
+      </c>
+      <c r="F26" t="n">
+        <v>139587226.4200174</v>
+      </c>
+      <c r="G26" t="n">
+        <v>99359777.75507279</v>
+      </c>
+      <c r="H26" t="n">
+        <v>73521643.66348314</v>
+      </c>
+      <c r="I26" t="n">
+        <v>139587226.4200174</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2017/e85bc3c6652e1ebf/provenance.json</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93959793.1477727</v>
+      </c>
+      <c r="C27" t="n">
+        <v>77766819.36422479</v>
+      </c>
+      <c r="D27" t="n">
+        <v>83828158.98644155</v>
+      </c>
+      <c r="E27" t="n">
+        <v>88871437.78305161</v>
+      </c>
+      <c r="F27" t="n">
+        <v>146333541.9822023</v>
+      </c>
+      <c r="G27" t="n">
+        <v>88871437.78305161</v>
+      </c>
+      <c r="H27" t="n">
+        <v>77766819.36422479</v>
+      </c>
+      <c r="I27" t="n">
+        <v>146333541.9822023</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2018/786b5184701484b9/provenance.json</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>5</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B28" t="n">
+        <v>102610079.5947482</v>
+      </c>
+      <c r="C28" t="n">
+        <v>88188091.76601842</v>
+      </c>
+      <c r="D28" t="n">
+        <v>95380030.60816732</v>
+      </c>
+      <c r="E28" t="n">
+        <v>108445890.0816866</v>
+      </c>
+      <c r="F28" t="n">
+        <v>158650294.4278253</v>
+      </c>
+      <c r="G28" t="n">
+        <v>102610079.5947482</v>
+      </c>
+      <c r="H28" t="n">
+        <v>88188091.76601842</v>
+      </c>
+      <c r="I28" t="n">
+        <v>158650294.4278253</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NPPExtraction/output/years/2019/e82a6f61f15e47c4/provenance.json</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>5</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>antoinemorel;vgpm;eppley;cbpm;cafe</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>common mask</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2475,188 +3788,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Specific PPR for LME_061</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>taxon</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>trophic_level</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>sppr_simple</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Rajiformes</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="C5" t="n">
-        <v>407.380278</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pagetodes antarcticus</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="C6" t="n">
-        <v>371.535229</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Macrourus whitsoni</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="C7" t="n">
-        <v>295.120923</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Neopagetopsis ionah</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="C8" t="n">
-        <v>263.026799</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Trematomus eulepidotus</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="C9" t="n">
-        <v>223.872114</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pogonophryne permitini</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="C10" t="n">
-        <v>194.98446</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Marine fishes not identified</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C11" t="n">
-        <v>190.546072</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pleuragramma antarcticum</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="C12" t="n">
-        <v>169.824365</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Artedidraconidae</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>125.892541</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mollusca</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>12.589254</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>so the network-based SPPR methods are not available here.</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>No final mappings are available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Models without a recorded mapping are not assigned invented taxon groups or weights.</t>
         </is>
       </c>
     </row>
@@ -2671,43 +3819,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Group SPPR: all</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>group_name</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Specific PPR for LME_061</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Simple method, applied per taxon: SPPR = (1/TE)^(TL-1), TE = 0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>taxon</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>trophic_level</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>sppr_simple</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No extracted model is available for this ecosystem.</t>
+          <t>Rajiformes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="C5" t="n">
+        <v>407.380278</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pagetodes antarcticus</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>371.535229</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Macrourus whitsoni</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="C7" t="n">
+        <v>295.120923</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Neopagetopsis ionah</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C8" t="n">
+        <v>263.026799</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trematomus eulepidotus</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C9" t="n">
+        <v>223.872114</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pogonophryne permitini</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C10" t="n">
+        <v>194.98446</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Marine fishes not identified</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C11" t="n">
+        <v>190.546072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pleuragramma antarcticum</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="C12" t="n">
+        <v>169.824365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Artedidraconidae</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>125.892541</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Mollusca</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12.589254</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>No Ecopath model has been extracted for this ecosystem yet,</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>so the network-based SPPR methods are not available here.</t>
         </is>
       </c>
     </row>
@@ -2732,14 +4025,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: inner</t>
+          <t>Group SPPR: all</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>All basal sources, including imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -2783,14 +4076,14 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Group SPPR: PP</t>
+          <t>Group SPPR: inner</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+          <t>Internal sources: primary producers and detritus; excludes imports. Models are separate. Blank means unavailable, not zero.</t>
         </is>
       </c>
     </row>
@@ -2819,6 +4112,57 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Group SPPR: PP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Primary producers only; excludes detritus and imports. Models are separate. Blank means unavailable, not zero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No extracted model is available for this ecosystem.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2904,7 +4248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3922,132 +5266,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Net primary production, 2019, tonnes carbon per year</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>satellite_model</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>npp_tC_yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Antoine-Morel</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>47870053.43602861</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>VGPM</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>41141851.57962558</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eppley</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>44497062.86142188</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CbPM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>50592598.44287</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAFE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>74014152.42923541</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ensemble median</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>47870053.43602861</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ensemble min</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>41141851.57962558</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ensemble max</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>74014152.42923541</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>water area (km2)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1783490.241453297</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>